--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:08</t>
+    <t xml:space="preserve">2026-09-09 23:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:02</t>
+    <t xml:space="preserve">2026-09-17 13:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:59</t>
+    <t xml:space="preserve">2026-09-23 12:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:28</t>
+    <t xml:space="preserve">2026-10-02 13:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:49</t>
+    <t xml:space="preserve">2026-10-04 08:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:50</t>
+    <t xml:space="preserve">2026-10-05 10:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -576,7 +576,7 @@
         <v>2020</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>825251.12</v>
+        <v>825251.13</v>
       </c>
     </row>
     <row r="7">
@@ -610,7 +610,7 @@
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>816090.62</v>
+        <v>816090.63</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
         <v>2020</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>751445.12</v>
+        <v>751445.13</v>
       </c>
     </row>
     <row r="10">
